--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92576752132</v>
+        <v>46157.93121846378</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93121846378</v>
+        <v>46157.93187557236</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93187557236</v>
+        <v>46157.93408322483</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93408322483</v>
+        <v>46157.93726044656</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93726044656</v>
+        <v>46158.28223579768</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28223579768</v>
+        <v>46158.29714990336</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29714990336</v>
+        <v>46158.29823930507</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29823930507</v>
+        <v>46158.33394671134</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33394671134</v>
+        <v>46158.36864394773</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Лопакова- руководитель соц. службы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36864394773</v>
+        <v>46158.37295381512</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
